--- a/DataAnalysis/TryingToPackStuffBetter/MLT/CI/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/MLT/CI/0.05/Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\MLT\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A272DD67-D754-4812-898B-FCDC06C7BF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D72396-462A-4066-8E69-CA7111109A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="33">
   <si>
     <t>ERR</t>
   </si>
@@ -100,9 +100,6 @@
     <t>CIC_STD</t>
   </si>
   <si>
-    <t>g=0.0001</t>
-  </si>
-  <si>
     <t>c0</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
     <t>ONLYMIN</t>
   </si>
   <si>
-    <t>try3</t>
-  </si>
-  <si>
     <t>Just out 0</t>
   </si>
 </sst>
@@ -184,8 +178,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -466,474 +461,419 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
       <c r="G1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="G4">
-        <v>14.214285714285714</v>
-      </c>
-      <c r="H4">
-        <v>2.0987524639084736</v>
-      </c>
-      <c r="I4">
+      <c r="F4" s="1">
+        <v>15.666666666666666</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2.42212028327799</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20.916666666666668</v>
+      </c>
+      <c r="I4" s="1">
+        <v>4.3979161732196186</v>
+      </c>
+      <c r="J4" s="1">
+        <v>28.75</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2.6220221204253789</v>
+      </c>
+      <c r="L4" s="1">
+        <v>21.777777777777775</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1.727768845993348</v>
+      </c>
+      <c r="N4" s="1">
+        <v>6.1111111111111098</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1.9739038214402216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1">
+        <v>14.25</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2.7703790354390136</v>
+      </c>
+      <c r="H5" s="1">
+        <v>19.166666666666668</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2.2060522810365799</v>
+      </c>
+      <c r="J5" s="1">
+        <v>27.583333333333332</v>
+      </c>
+      <c r="K5" s="1">
+        <v>2.9396711834262463</v>
+      </c>
+      <c r="L5" s="1">
+        <v>20.333333333333332</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1.2064640713902566</v>
+      </c>
+      <c r="N5" s="1">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="O5" s="1">
+        <v>2.8616234708446333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="J4">
-        <v>2.5495097567963922</v>
-      </c>
-      <c r="K4">
-        <v>31.428571428571427</v>
-      </c>
-      <c r="L4">
-        <v>5.2870011303555522</v>
-      </c>
-      <c r="M4">
-        <v>22.88095238095238</v>
-      </c>
-      <c r="N4">
-        <v>2.2601914981845255</v>
-      </c>
-      <c r="O4">
-        <v>8.6666666666666661</v>
-      </c>
-      <c r="P4">
-        <v>2.0971762320196583</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1">
+        <v>17.142857142857142</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.625686668105863</v>
+      </c>
+      <c r="H7" s="1">
+        <v>17.142857142857142</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2.7945525240230817</v>
+      </c>
+      <c r="J7" s="1">
+        <v>29.571428571428573</v>
+      </c>
+      <c r="K7" s="1">
+        <v>4.1071946166510731</v>
+      </c>
+      <c r="L7" s="1">
+        <v>21.285714285714288</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2.4204267409829603</v>
+      </c>
+      <c r="N7" s="1">
+        <v>5.0714285714285712</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1.5865672904720345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1">
+        <v>15.083333333333334</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4.7054932437170338</v>
+      </c>
+      <c r="H9" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>3.7815340802378077</v>
+      </c>
+      <c r="J9" s="1">
+        <v>26.833333333333332</v>
+      </c>
+      <c r="K9" s="1">
+        <v>3.2197308376115243</v>
+      </c>
+      <c r="L9" s="1">
+        <v>20.138888888888889</v>
+      </c>
+      <c r="M9" s="1">
+        <v>2.9541245491434216</v>
+      </c>
+      <c r="N9" s="1">
+        <v>5.4722222222222214</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1.8571682944940902</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5">
-        <v>14.916666666666666</v>
-      </c>
-      <c r="H5">
-        <v>2.1775368347439388</v>
-      </c>
-      <c r="I5">
-        <v>20.416666666666668</v>
-      </c>
-      <c r="J5">
-        <v>2.4983327774071045</v>
-      </c>
-      <c r="K5">
-        <v>26.416666666666668</v>
-      </c>
-      <c r="L5">
-        <v>1.4288690166235207</v>
-      </c>
-      <c r="M5">
-        <v>20.583333333333332</v>
-      </c>
-      <c r="N5">
-        <v>1.0368220676663862</v>
-      </c>
-      <c r="O5">
-        <v>5.666666666666667</v>
-      </c>
-      <c r="P5">
-        <v>1.7224014243685055</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>18.7</v>
-      </c>
-      <c r="H7">
-        <v>2.7748873851023195</v>
-      </c>
-      <c r="I7">
-        <v>18.5</v>
-      </c>
-      <c r="J7">
-        <v>1.541103500742244</v>
-      </c>
-      <c r="K7">
-        <v>27.5</v>
-      </c>
-      <c r="L7">
-        <v>1.2247448713915889</v>
-      </c>
-      <c r="M7">
-        <v>21.566666666666666</v>
-      </c>
-      <c r="N7">
-        <v>1.4841757907262121</v>
-      </c>
-      <c r="O7">
-        <v>3.9666666666666663</v>
-      </c>
-      <c r="P7">
-        <v>0.74907350180814036</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8">
-        <v>16.5</v>
-      </c>
-      <c r="H8">
-        <v>0.70710678118654757</v>
-      </c>
-      <c r="I8">
-        <v>17.25</v>
-      </c>
-      <c r="J8">
-        <v>3.378855822118882</v>
-      </c>
-      <c r="K8">
-        <v>31.25</v>
-      </c>
-      <c r="L8">
-        <v>3.1754264805429417</v>
-      </c>
-      <c r="M8">
-        <v>21.6666666666667</v>
-      </c>
-      <c r="N8">
-        <v>2.2730302828309759</v>
-      </c>
-      <c r="O8">
-        <v>5.7916666666666679</v>
-      </c>
-      <c r="P8">
-        <v>1.6007810593582092</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10">
-        <v>15.625</v>
-      </c>
-      <c r="H10">
-        <v>1.6007810593582121</v>
-      </c>
-      <c r="I10">
-        <v>18.625</v>
-      </c>
-      <c r="J10">
-        <v>2.75</v>
-      </c>
-      <c r="K10">
-        <v>26.625</v>
-      </c>
-      <c r="L10">
-        <v>4.6435439052516774</v>
-      </c>
-      <c r="M10">
-        <v>20.291666666666668</v>
-      </c>
-      <c r="N10">
-        <v>1.8923579255834544</v>
-      </c>
-      <c r="O10">
-        <v>4.791666666666667</v>
-      </c>
-      <c r="P10">
-        <v>1.7393858004948073</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11">
-        <v>14.875</v>
-      </c>
-      <c r="H11">
-        <v>4.0697051490249265</v>
-      </c>
-      <c r="I11">
-        <v>16.5</v>
-      </c>
-      <c r="J11">
-        <v>2.2730302828309759</v>
-      </c>
-      <c r="K11">
-        <v>27</v>
-      </c>
-      <c r="L11">
-        <v>3.3416562759605704</v>
-      </c>
-      <c r="M11">
-        <v>19.458333333333332</v>
-      </c>
-      <c r="N11">
-        <v>2.1273135553939757</v>
-      </c>
-      <c r="O11">
-        <v>5.2083333333333304</v>
-      </c>
-      <c r="P11">
-        <v>1.674288129546627</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>17.071428571428573</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2.149196970742242</v>
+      </c>
+      <c r="H12" s="1">
+        <v>16.857142857142858</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3.1320159337914957</v>
+      </c>
+      <c r="J12" s="1">
+        <v>30.928571428571427</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3.7906526639943623</v>
+      </c>
+      <c r="L12" s="1">
+        <v>21.619047619047617</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1.0350983390135315</v>
+      </c>
+      <c r="N12" s="1">
+        <v>5.7619047619047636</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1.6690459207925552</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="1">
+        <v>17.333333333333332</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4.1912607490666396</v>
+      </c>
+      <c r="H13" s="1">
+        <v>15.583333333333334</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2.8533605917701061</v>
+      </c>
+      <c r="J13" s="1">
+        <v>29.083333333333332</v>
+      </c>
+      <c r="K13" s="1">
+        <v>4.1882772910430139</v>
+      </c>
+      <c r="L13" s="1">
+        <v>20.666666666666668</v>
+      </c>
+      <c r="M13" s="1">
+        <v>2.7487370837451088</v>
+      </c>
+      <c r="N13" s="1">
+        <v>5.916666666666667</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1.6012148165967275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="1">
+        <v>16.611111111111111</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.0240171439537089</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16.833333333333332</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2.4874685927665499</v>
+      </c>
+      <c r="J15" s="1">
+        <v>29.833333333333332</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2.1360009363293826</v>
+      </c>
+      <c r="L15" s="1">
+        <v>21.092592592592595</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0.96144823888204367</v>
+      </c>
+      <c r="N15" s="1">
+        <v>5.314814814814814</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1.3955396318978317</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>16.416666666666668</v>
-      </c>
-      <c r="H13">
-        <v>2.8881943609574914</v>
-      </c>
-      <c r="I13">
-        <v>15.416666666666666</v>
-      </c>
-      <c r="J13">
-        <v>1.2812754062521714</v>
-      </c>
-      <c r="K13">
-        <v>29.916666666666668</v>
-      </c>
-      <c r="L13">
-        <v>2.437553418218084</v>
-      </c>
-      <c r="M13">
-        <v>20.583333333333332</v>
-      </c>
-      <c r="N13">
-        <v>1.3570801990548194</v>
-      </c>
-      <c r="O13">
-        <v>5.916666666666667</v>
-      </c>
-      <c r="P13">
-        <v>1.0527741131569135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14">
-        <v>16.8</v>
-      </c>
-      <c r="H14">
-        <v>0.57008771254956903</v>
-      </c>
-      <c r="I14">
-        <v>17.7</v>
-      </c>
-      <c r="J14">
-        <v>1.7175564037317668</v>
-      </c>
-      <c r="K14">
-        <v>28.9</v>
-      </c>
-      <c r="L14">
-        <v>3.8794329482541587</v>
-      </c>
-      <c r="M14">
-        <v>21.133333333333333</v>
-      </c>
-      <c r="N14">
-        <v>1.5696779570628134</v>
-      </c>
-      <c r="O14">
-        <v>4.7333333333333325</v>
-      </c>
-      <c r="P14">
-        <v>0.90215790684828923</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17">
-        <v>16</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>15.75</v>
-      </c>
-      <c r="J17">
-        <v>4.5961940777125587</v>
-      </c>
-      <c r="K17">
-        <v>30</v>
-      </c>
-      <c r="L17">
-        <v>3.5355339059327378</v>
-      </c>
-      <c r="M17">
-        <v>20.583333333333332</v>
-      </c>
-      <c r="N17">
-        <v>0.35355339059327379</v>
-      </c>
-      <c r="O17">
-        <v>6.3333333333333321</v>
-      </c>
-      <c r="P17">
-        <v>2.1213203435596459</v>
-      </c>
-    </row>
-    <row r="18" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19">
-        <v>16.375</v>
-      </c>
-      <c r="H19">
-        <v>3.3008837200563934</v>
-      </c>
-      <c r="I19">
-        <v>20</v>
-      </c>
-      <c r="J19">
-        <v>3.3166247903553998</v>
-      </c>
-      <c r="K19">
-        <v>26.875</v>
-      </c>
-      <c r="L19">
-        <v>1.796988221070652</v>
-      </c>
-      <c r="M19">
-        <v>21.083333333333332</v>
-      </c>
-      <c r="N19">
-        <v>1.5898986690282424</v>
-      </c>
-      <c r="O19">
-        <v>4.708333333333333</v>
-      </c>
-      <c r="P19">
-        <v>2.9071272570854019</v>
-      </c>
-    </row>
-    <row r="20" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F20" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20">
-        <v>14.333333333333334</v>
-      </c>
-      <c r="H20">
-        <v>3.2145502536643153</v>
-      </c>
-      <c r="I20">
-        <v>17.166666666666668</v>
-      </c>
-      <c r="J20">
-        <v>1.2583057392117916</v>
-      </c>
-      <c r="K20">
-        <v>26.6666666666667</v>
-      </c>
-      <c r="L20">
-        <v>4.1633319989322564</v>
-      </c>
-      <c r="M20">
-        <v>19.3888888888889</v>
-      </c>
-      <c r="N20">
-        <v>2.4962935487400935</v>
-      </c>
-      <c r="O20">
-        <v>5.0555555555555562</v>
-      </c>
-      <c r="P20">
-        <v>1.3977495139343468</v>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2.5884358211089546</v>
+      </c>
+      <c r="H17" s="1">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1.3874436925511606</v>
+      </c>
+      <c r="J17" s="1">
+        <v>27.8</v>
+      </c>
+      <c r="K17" s="1">
+        <v>3.9465174521342288</v>
+      </c>
+      <c r="L17" s="1">
+        <v>19.733333333333334</v>
+      </c>
+      <c r="M17" s="1">
+        <v>1.9811612756158952</v>
+      </c>
+      <c r="N17" s="1">
+        <v>5.5333333333333332</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1.2213380640374176</v>
       </c>
     </row>
   </sheetData>
@@ -944,18 +884,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
-  <dimension ref="A2:AF3"/>
+  <dimension ref="A2:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>9</v>
@@ -976,22 +916,22 @@
         <v>12</v>
       </c>
       <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>22</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>23</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
@@ -1007,69 +947,703 @@
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q3" t="e">
+      <c r="B3">
+        <v>94</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>82</v>
+      </c>
+      <c r="G3">
+        <v>79</v>
+      </c>
+      <c r="H3">
+        <v>21</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>89</v>
+      </c>
+      <c r="L3">
+        <v>60</v>
+      </c>
+      <c r="M3">
+        <v>40</v>
+      </c>
+      <c r="N3">
+        <v>16</v>
+      </c>
+      <c r="O3">
+        <v>84</v>
+      </c>
+      <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R3" t="e">
+        <v>12</v>
+      </c>
+      <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S3" t="e">
+        <v>16</v>
+      </c>
+      <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" t="e">
+        <v>28</v>
+      </c>
+      <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U3" t="e">
+        <v>18.666666666666668</v>
+      </c>
+      <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V3" t="e">
+        <v>12</v>
+      </c>
+      <c r="V3">
         <f>T3-U3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W3" t="e">
+        <v>6.6666666666666679</v>
+      </c>
+      <c r="W3">
         <f>AVERAGE(Q3:Q8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X3" t="e">
+        <v>14.3</v>
+      </c>
+      <c r="X3">
         <f>_xlfn.STDEV.S(Q3:Q8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y3" t="e">
+        <v>2.5884358211089546</v>
+      </c>
+      <c r="Y3">
         <f>AVERAGE(R3:R8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z3" t="e">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="Z3">
         <f>_xlfn.STDEV.S(R3:R8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA3" t="e">
+        <v>1.3874436925511606</v>
+      </c>
+      <c r="AA3">
         <f>AVERAGE(S3:S8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB3" t="e">
+        <v>27.8</v>
+      </c>
+      <c r="AB3">
         <f>_xlfn.STDEV.S(S3:S8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC3" t="e">
+        <v>3.9465174521342288</v>
+      </c>
+      <c r="AC3">
         <f>AVERAGE(T3:T8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD3" t="e">
+        <v>19.733333333333334</v>
+      </c>
+      <c r="AD3">
         <f>_xlfn.STDEV.S(T3:T8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE3" t="e">
+        <v>1.9811612756158952</v>
+      </c>
+      <c r="AE3">
         <f>AVERAGE(V3:V8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF3" t="e">
+        <v>5.5333333333333332</v>
+      </c>
+      <c r="AF3">
         <f>_xlfn.STDEV.S(V3:V8)</f>
-        <v>#DIV/0!</v>
+        <v>1.2213380640374176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>86</v>
+      </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>78</v>
+      </c>
+      <c r="G4">
+        <v>81</v>
+      </c>
+      <c r="H4">
+        <v>19</v>
+      </c>
+      <c r="I4">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>82</v>
+      </c>
+      <c r="L4">
+        <v>78</v>
+      </c>
+      <c r="M4">
+        <v>22</v>
+      </c>
+      <c r="N4">
+        <v>38</v>
+      </c>
+      <c r="O4">
+        <v>62</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q8" si="0">AVERAGE(C4:D4)</f>
+        <v>18</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R8" si="1">AVERAGE(H4:I4)</f>
+        <v>18.5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S8" si="2">AVERAGE(M4:N4)</f>
+        <v>30</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T8" si="3">AVERAGE(Q4:S4)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U8" si="4">MIN(Q4:S4)</f>
+        <v>18</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V8" si="5">T4-U4</f>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>91</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>83</v>
+      </c>
+      <c r="G5">
+        <v>79</v>
+      </c>
+      <c r="H5">
+        <v>21</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>87</v>
+      </c>
+      <c r="L5">
+        <v>74</v>
+      </c>
+      <c r="M5">
+        <v>26</v>
+      </c>
+      <c r="N5">
+        <v>18</v>
+      </c>
+      <c r="O5">
+        <v>82</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>4.3333333333333321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>95</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>76</v>
+      </c>
+      <c r="H6">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>87</v>
+      </c>
+      <c r="L6">
+        <v>73</v>
+      </c>
+      <c r="M6">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>26</v>
+      </c>
+      <c r="O6">
+        <v>74</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>26.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>6.6666666666666679</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>91</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>77</v>
+      </c>
+      <c r="G7">
+        <v>76</v>
+      </c>
+      <c r="H7">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>93</v>
+      </c>
+      <c r="L7">
+        <v>71</v>
+      </c>
+      <c r="M7">
+        <v>29</v>
+      </c>
+      <c r="N7">
+        <v>36</v>
+      </c>
+      <c r="O7">
+        <v>64</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>15.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>5.8333333333333321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>82</v>
+      </c>
+      <c r="G10">
+        <v>79</v>
+      </c>
+      <c r="H10">
+        <v>21</v>
+      </c>
+      <c r="I10">
+        <v>11</v>
+      </c>
+      <c r="J10">
+        <v>89</v>
+      </c>
+      <c r="L10">
+        <v>60</v>
+      </c>
+      <c r="M10">
+        <v>40</v>
+      </c>
+      <c r="N10">
+        <v>16</v>
+      </c>
+      <c r="O10">
+        <v>84</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ref="Q9:Q14" si="6">AVERAGE(C10:D10)</f>
+        <v>12</v>
+      </c>
+      <c r="R10">
+        <f t="shared" ref="R9:R14" si="7">AVERAGE(H10:I10)</f>
+        <v>16</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S9:S14" si="8">AVERAGE(M10:N10)</f>
+        <v>28</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T9:T14" si="9">AVERAGE(Q10:S10)</f>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="U10">
+        <f t="shared" ref="U9:U14" si="10">MIN(Q10:S10)</f>
+        <v>12</v>
+      </c>
+      <c r="V10">
+        <f t="shared" ref="V9:V14" si="11">T10-U10</f>
+        <v>6.6666666666666679</v>
+      </c>
+      <c r="W10">
+        <f>AVERAGE(Q10:Q15)</f>
+        <v>14.3</v>
+      </c>
+      <c r="X10">
+        <f>_xlfn.STDEV.S(Q10:Q15)</f>
+        <v>2.5884358211089546</v>
+      </c>
+      <c r="Y10">
+        <f>AVERAGE(R10:R15)</f>
+        <v>17.100000000000001</v>
+      </c>
+      <c r="Z10">
+        <f>_xlfn.STDEV.S(R10:R15)</f>
+        <v>1.3874436925511606</v>
+      </c>
+      <c r="AA10">
+        <f>AVERAGE(S10:S15)</f>
+        <v>27.8</v>
+      </c>
+      <c r="AB10">
+        <f>_xlfn.STDEV.S(S10:S15)</f>
+        <v>3.9465174521342288</v>
+      </c>
+      <c r="AC10">
+        <f>AVERAGE(T10:T15)</f>
+        <v>19.733333333333334</v>
+      </c>
+      <c r="AD10">
+        <f>_xlfn.STDEV.S(T10:T15)</f>
+        <v>1.9811612756158952</v>
+      </c>
+      <c r="AE10">
+        <f>AVERAGE(V10:V15)</f>
+        <v>5.5333333333333332</v>
+      </c>
+      <c r="AF10">
+        <f>_xlfn.STDEV.S(V10:V15)</f>
+        <v>1.2213380640374176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <v>78</v>
+      </c>
+      <c r="G11">
+        <v>81</v>
+      </c>
+      <c r="H11">
+        <v>19</v>
+      </c>
+      <c r="I11">
+        <v>18</v>
+      </c>
+      <c r="J11">
+        <v>82</v>
+      </c>
+      <c r="L11">
+        <v>78</v>
+      </c>
+      <c r="M11">
+        <v>22</v>
+      </c>
+      <c r="N11">
+        <v>38</v>
+      </c>
+      <c r="O11">
+        <v>62</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="11"/>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>91</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>17</v>
+      </c>
+      <c r="E12">
+        <v>83</v>
+      </c>
+      <c r="G12">
+        <v>79</v>
+      </c>
+      <c r="H12">
+        <v>21</v>
+      </c>
+      <c r="I12">
+        <v>13</v>
+      </c>
+      <c r="J12">
+        <v>87</v>
+      </c>
+      <c r="L12">
+        <v>74</v>
+      </c>
+      <c r="M12">
+        <v>26</v>
+      </c>
+      <c r="N12">
+        <v>18</v>
+      </c>
+      <c r="O12">
+        <v>82</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>22</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="11"/>
+        <v>4.3333333333333321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>95</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>76</v>
+      </c>
+      <c r="H13">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>13</v>
+      </c>
+      <c r="J13">
+        <v>87</v>
+      </c>
+      <c r="L13">
+        <v>73</v>
+      </c>
+      <c r="M13">
+        <v>27</v>
+      </c>
+      <c r="N13">
+        <v>26</v>
+      </c>
+      <c r="O13">
+        <v>74</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>12.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>26.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="11"/>
+        <v>6.6666666666666679</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>91</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>23</v>
+      </c>
+      <c r="E14">
+        <v>77</v>
+      </c>
+      <c r="G14">
+        <v>76</v>
+      </c>
+      <c r="H14">
+        <v>24</v>
+      </c>
+      <c r="I14">
+        <v>7</v>
+      </c>
+      <c r="J14">
+        <v>93</v>
+      </c>
+      <c r="L14">
+        <v>71</v>
+      </c>
+      <c r="M14">
+        <v>29</v>
+      </c>
+      <c r="N14">
+        <v>36</v>
+      </c>
+      <c r="O14">
+        <v>64</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>15.5</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>32.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="11"/>
+        <v>5.8333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -1079,18 +1653,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5294201-0F1E-4EFB-96A1-05886F39E142}">
-  <dimension ref="A2:AF3"/>
+  <dimension ref="A2:AF22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>9</v>
@@ -1111,22 +1685,22 @@
         <v>12</v>
       </c>
       <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>22</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>23</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
@@ -1142,69 +1716,1199 @@
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q3" t="e">
+      <c r="B3">
+        <v>81</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>87</v>
+      </c>
+      <c r="G3">
+        <v>78</v>
+      </c>
+      <c r="H3">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>97</v>
+      </c>
+      <c r="L3">
+        <v>65</v>
+      </c>
+      <c r="M3">
+        <v>35</v>
+      </c>
+      <c r="N3">
+        <v>30</v>
+      </c>
+      <c r="O3">
+        <v>70</v>
+      </c>
+      <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R3" t="e">
+        <v>16</v>
+      </c>
+      <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S3" t="e">
+        <v>12.5</v>
+      </c>
+      <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" t="e">
+        <v>32.5</v>
+      </c>
+      <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U3" t="e">
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V3" t="e">
+        <v>12.5</v>
+      </c>
+      <c r="V3">
         <f>T3-U3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W3" t="e">
-        <f>AVERAGE(Q3:Q8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X3" t="e">
-        <f>_xlfn.STDEV.S(Q3:Q8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y3" t="e">
-        <f>AVERAGE(R3:R8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z3" t="e">
-        <f>_xlfn.STDEV.S(R3:R8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA3" t="e">
-        <f>AVERAGE(S3:S8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB3" t="e">
-        <f>_xlfn.STDEV.S(S3:S8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC3" t="e">
-        <f>AVERAGE(T3:T8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD3" t="e">
-        <f>_xlfn.STDEV.S(T3:T8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE3" t="e">
-        <f>AVERAGE(V3:V8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF3" t="e">
-        <f>_xlfn.STDEV.S(V3:V8)</f>
-        <v>#DIV/0!</v>
+        <v>7.8333333333333321</v>
+      </c>
+      <c r="W3">
+        <f>AVERAGE(Q3:Q11)</f>
+        <v>16.611111111111111</v>
+      </c>
+      <c r="X3">
+        <f>_xlfn.STDEV.S(Q3:Q11)</f>
+        <v>1.0240171439537089</v>
+      </c>
+      <c r="Y3">
+        <f>AVERAGE(R3:R11)</f>
+        <v>16.833333333333332</v>
+      </c>
+      <c r="Z3">
+        <f>_xlfn.STDEV.S(R3:R11)</f>
+        <v>2.4874685927665499</v>
+      </c>
+      <c r="AA3">
+        <f>AVERAGE(S3:S11)</f>
+        <v>29.833333333333332</v>
+      </c>
+      <c r="AB3">
+        <f>_xlfn.STDEV.S(S3:S11)</f>
+        <v>2.1360009363293826</v>
+      </c>
+      <c r="AC3">
+        <f>AVERAGE(T3:T11)</f>
+        <v>21.092592592592595</v>
+      </c>
+      <c r="AD3">
+        <f>_xlfn.STDEV.S(T3:T11)</f>
+        <v>0.96144823888204367</v>
+      </c>
+      <c r="AE3">
+        <f>AVERAGE(V3:V11)</f>
+        <v>5.314814814814814</v>
+      </c>
+      <c r="AF3">
+        <f>_xlfn.STDEV.S(V3:V11)</f>
+        <v>1.3955396318978317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>88</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <v>80</v>
+      </c>
+      <c r="H4">
+        <v>20</v>
+      </c>
+      <c r="I4">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>82</v>
+      </c>
+      <c r="L4">
+        <v>72</v>
+      </c>
+      <c r="M4">
+        <v>28</v>
+      </c>
+      <c r="N4">
+        <v>27</v>
+      </c>
+      <c r="O4">
+        <v>73</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q11" si="0">AVERAGE(C4:D4)</f>
+        <v>16</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R11" si="1">AVERAGE(H4:I4)</f>
+        <v>19</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S11" si="2">AVERAGE(M4:N4)</f>
+        <v>27.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T11" si="3">AVERAGE(Q4:S4)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U11" si="4">MIN(Q4:S4)</f>
+        <v>16</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V11" si="5">T4-U4</f>
+        <v>4.8333333333333321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>87</v>
+      </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>78</v>
+      </c>
+      <c r="G5">
+        <v>66</v>
+      </c>
+      <c r="H5">
+        <v>34</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>96</v>
+      </c>
+      <c r="L5">
+        <v>66</v>
+      </c>
+      <c r="M5">
+        <v>34</v>
+      </c>
+      <c r="N5">
+        <v>23</v>
+      </c>
+      <c r="O5">
+        <v>77</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>28.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>17.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>84</v>
+      </c>
+      <c r="G6">
+        <v>70</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>90</v>
+      </c>
+      <c r="L6">
+        <v>67</v>
+      </c>
+      <c r="M6">
+        <v>33</v>
+      </c>
+      <c r="N6">
+        <v>29</v>
+      </c>
+      <c r="O6">
+        <v>71</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>87</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>71</v>
+      </c>
+      <c r="H7">
+        <v>29</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>95</v>
+      </c>
+      <c r="L7">
+        <v>72</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
+      </c>
+      <c r="N7">
+        <v>36</v>
+      </c>
+      <c r="O7">
+        <v>64</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>83</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>83</v>
+      </c>
+      <c r="G8">
+        <v>79</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>94</v>
+      </c>
+      <c r="L8">
+        <v>65</v>
+      </c>
+      <c r="M8">
+        <v>35</v>
+      </c>
+      <c r="N8">
+        <v>28</v>
+      </c>
+      <c r="O8">
+        <v>72</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>13.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>31.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>13.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>7.1666666666666679</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>91</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>79</v>
+      </c>
+      <c r="G9">
+        <v>75</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>92</v>
+      </c>
+      <c r="L9">
+        <v>80</v>
+      </c>
+      <c r="M9">
+        <v>20</v>
+      </c>
+      <c r="N9">
+        <v>37</v>
+      </c>
+      <c r="O9">
+        <v>63</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>28.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>90</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>79</v>
+      </c>
+      <c r="G10">
+        <v>77</v>
+      </c>
+      <c r="H10">
+        <v>23</v>
+      </c>
+      <c r="I10">
+        <v>11</v>
+      </c>
+      <c r="J10">
+        <v>89</v>
+      </c>
+      <c r="L10">
+        <v>74</v>
+      </c>
+      <c r="M10">
+        <v>26</v>
+      </c>
+      <c r="N10">
+        <v>35</v>
+      </c>
+      <c r="O10">
+        <v>65</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>22</v>
+      </c>
+      <c r="D11">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>87</v>
+      </c>
+      <c r="G11">
+        <v>69</v>
+      </c>
+      <c r="H11">
+        <v>31</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>97</v>
+      </c>
+      <c r="L11">
+        <v>71</v>
+      </c>
+      <c r="M11">
+        <v>29</v>
+      </c>
+      <c r="N11">
+        <v>24</v>
+      </c>
+      <c r="O11">
+        <v>76</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>26.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>3.3333333333333321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>87</v>
+      </c>
+      <c r="G14">
+        <v>78</v>
+      </c>
+      <c r="H14">
+        <v>22</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>97</v>
+      </c>
+      <c r="L14">
+        <v>65</v>
+      </c>
+      <c r="M14">
+        <v>35</v>
+      </c>
+      <c r="N14">
+        <v>29</v>
+      </c>
+      <c r="O14">
+        <v>71</v>
+      </c>
+      <c r="Q14">
+        <f>AVERAGE(C14:D14)</f>
+        <v>16</v>
+      </c>
+      <c r="R14">
+        <f>AVERAGE(H14:I14)</f>
+        <v>12.5</v>
+      </c>
+      <c r="S14">
+        <f>AVERAGE(M14:N14)</f>
+        <v>32</v>
+      </c>
+      <c r="T14">
+        <f>AVERAGE(Q14:S14)</f>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U14">
+        <f>MIN(Q14:S14)</f>
+        <v>12.5</v>
+      </c>
+      <c r="V14">
+        <f>T14-U14</f>
+        <v>7.6666666666666679</v>
+      </c>
+      <c r="W14">
+        <f>AVERAGE(Q14:Q22)</f>
+        <v>16.611111111111111</v>
+      </c>
+      <c r="X14">
+        <f>_xlfn.STDEV.S(Q14:Q22)</f>
+        <v>1.0240171439537089</v>
+      </c>
+      <c r="Y14">
+        <f>AVERAGE(R14:R22)</f>
+        <v>16.888888888888889</v>
+      </c>
+      <c r="Z14">
+        <f>_xlfn.STDEV.S(R14:R22)</f>
+        <v>2.5467844649893494</v>
+      </c>
+      <c r="AA14">
+        <f>AVERAGE(S14:S22)</f>
+        <v>29.888888888888889</v>
+      </c>
+      <c r="AB14">
+        <f>_xlfn.STDEV.S(S14:S22)</f>
+        <v>2.1762608095334324</v>
+      </c>
+      <c r="AC14">
+        <f>AVERAGE(T14:T22)</f>
+        <v>21.12962962962963</v>
+      </c>
+      <c r="AD14">
+        <f>_xlfn.STDEV.S(T14:T22)</f>
+        <v>0.99574712938527321</v>
+      </c>
+      <c r="AE14">
+        <f>AVERAGE(V14:V22)</f>
+        <v>5.3518518518518521</v>
+      </c>
+      <c r="AF14">
+        <f>_xlfn.STDEV.S(V14:V22)</f>
+        <v>1.3905545567537574</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>88</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>80</v>
+      </c>
+      <c r="G15">
+        <v>80</v>
+      </c>
+      <c r="H15">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>19</v>
+      </c>
+      <c r="J15">
+        <v>81</v>
+      </c>
+      <c r="L15">
+        <v>73</v>
+      </c>
+      <c r="M15">
+        <v>27</v>
+      </c>
+      <c r="N15">
+        <v>29</v>
+      </c>
+      <c r="O15">
+        <v>71</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" ref="Q15:Q22" si="6">AVERAGE(C15:D15)</f>
+        <v>16</v>
+      </c>
+      <c r="R15">
+        <f t="shared" ref="R15:R22" si="7">AVERAGE(H15:I15)</f>
+        <v>19.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" ref="S15:S22" si="8">AVERAGE(M15:N15)</f>
+        <v>28</v>
+      </c>
+      <c r="T15">
+        <f t="shared" ref="T15:T22" si="9">AVERAGE(Q15:S15)</f>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U15">
+        <f t="shared" ref="U15:U22" si="10">MIN(Q15:S15)</f>
+        <v>16</v>
+      </c>
+      <c r="V15">
+        <f t="shared" ref="V15:V22" si="11">T15-U15</f>
+        <v>5.1666666666666679</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>87</v>
+      </c>
+      <c r="C16">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>22</v>
+      </c>
+      <c r="E16">
+        <v>78</v>
+      </c>
+      <c r="G16">
+        <v>66</v>
+      </c>
+      <c r="H16">
+        <v>34</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16">
+        <v>96</v>
+      </c>
+      <c r="L16">
+        <v>66</v>
+      </c>
+      <c r="M16">
+        <v>34</v>
+      </c>
+      <c r="N16">
+        <v>23</v>
+      </c>
+      <c r="O16">
+        <v>77</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>17.5</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="8"/>
+        <v>28.5</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="9"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="10"/>
+        <v>17.5</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="11"/>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>80</v>
+      </c>
+      <c r="C17">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>84</v>
+      </c>
+      <c r="G17">
+        <v>70</v>
+      </c>
+      <c r="H17">
+        <v>30</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>90</v>
+      </c>
+      <c r="L17">
+        <v>67</v>
+      </c>
+      <c r="M17">
+        <v>33</v>
+      </c>
+      <c r="N17">
+        <v>29</v>
+      </c>
+      <c r="O17">
+        <v>71</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="9"/>
+        <v>23</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>87</v>
+      </c>
+      <c r="C18">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>21</v>
+      </c>
+      <c r="E18">
+        <v>79</v>
+      </c>
+      <c r="G18">
+        <v>71</v>
+      </c>
+      <c r="H18">
+        <v>29</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>95</v>
+      </c>
+      <c r="L18">
+        <v>72</v>
+      </c>
+      <c r="M18">
+        <v>28</v>
+      </c>
+      <c r="N18">
+        <v>36</v>
+      </c>
+      <c r="O18">
+        <v>64</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="8"/>
+        <v>32</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="9"/>
+        <v>22</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>83</v>
+      </c>
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19">
+        <v>83</v>
+      </c>
+      <c r="G19">
+        <v>79</v>
+      </c>
+      <c r="H19">
+        <v>21</v>
+      </c>
+      <c r="I19">
+        <v>6</v>
+      </c>
+      <c r="J19">
+        <v>94</v>
+      </c>
+      <c r="L19">
+        <v>65</v>
+      </c>
+      <c r="M19">
+        <v>35</v>
+      </c>
+      <c r="N19">
+        <v>28</v>
+      </c>
+      <c r="O19">
+        <v>72</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="7"/>
+        <v>13.5</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="8"/>
+        <v>31.5</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="9"/>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="11"/>
+        <v>7.1666666666666679</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>91</v>
+      </c>
+      <c r="C20">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>21</v>
+      </c>
+      <c r="E20">
+        <v>79</v>
+      </c>
+      <c r="G20">
+        <v>75</v>
+      </c>
+      <c r="H20">
+        <v>25</v>
+      </c>
+      <c r="I20">
+        <v>8</v>
+      </c>
+      <c r="J20">
+        <v>92</v>
+      </c>
+      <c r="L20">
+        <v>80</v>
+      </c>
+      <c r="M20">
+        <v>20</v>
+      </c>
+      <c r="N20">
+        <v>37</v>
+      </c>
+      <c r="O20">
+        <v>63</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="8"/>
+        <v>28.5</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>90</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>21</v>
+      </c>
+      <c r="E21">
+        <v>79</v>
+      </c>
+      <c r="G21">
+        <v>77</v>
+      </c>
+      <c r="H21">
+        <v>23</v>
+      </c>
+      <c r="I21">
+        <v>11</v>
+      </c>
+      <c r="J21">
+        <v>89</v>
+      </c>
+      <c r="L21">
+        <v>72</v>
+      </c>
+      <c r="M21">
+        <v>28</v>
+      </c>
+      <c r="N21">
+        <v>35</v>
+      </c>
+      <c r="O21">
+        <v>65</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="8"/>
+        <v>31.5</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="9"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="11"/>
+        <v>5.8333333333333321</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>78</v>
+      </c>
+      <c r="C22">
+        <v>22</v>
+      </c>
+      <c r="D22">
+        <v>13</v>
+      </c>
+      <c r="E22">
+        <v>87</v>
+      </c>
+      <c r="G22">
+        <v>69</v>
+      </c>
+      <c r="H22">
+        <v>31</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>97</v>
+      </c>
+      <c r="L22">
+        <v>72</v>
+      </c>
+      <c r="M22">
+        <v>28</v>
+      </c>
+      <c r="N22">
+        <v>24</v>
+      </c>
+      <c r="O22">
+        <v>76</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="6"/>
+        <v>17.5</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="8"/>
+        <v>26</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="9"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="11"/>
+        <v>3.1666666666666679</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +2918,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1341680-B8DF-484F-AD8E-90C5FE6FD057}">
-  <dimension ref="B1:AF2"/>
+  <dimension ref="B1:AF16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:32" x14ac:dyDescent="0.3">
@@ -1237,22 +2941,22 @@
         <v>12</v>
       </c>
       <c r="W1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" t="s">
         <v>25</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>22</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>23</v>
       </c>
       <c r="AC1" t="s">
         <v>0</v>
@@ -1269,108 +2973,831 @@
     </row>
     <row r="2" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="L2">
+        <v>74</v>
+      </c>
+      <c r="M2">
+        <v>26</v>
+      </c>
+      <c r="N2">
+        <v>35</v>
+      </c>
+      <c r="O2">
         <v>65</v>
-      </c>
-      <c r="M2">
-        <v>35</v>
-      </c>
-      <c r="N2">
-        <v>30</v>
-      </c>
-      <c r="O2">
-        <v>70</v>
       </c>
       <c r="Q2">
         <f>AVERAGE(C2:D2)</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="R2">
         <f>AVERAGE(H2:I2)</f>
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="S2">
         <f>AVERAGE(M2:N2)</f>
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="T2">
         <f>AVERAGE(Q2:S2)</f>
-        <v>20.333333333333332</v>
+        <v>24.166666666666668</v>
       </c>
       <c r="U2">
         <f>MIN(Q2:S2)</f>
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="V2">
         <f>T2-U2</f>
-        <v>7.8333333333333321</v>
+        <v>4.1666666666666679</v>
       </c>
       <c r="W2">
         <f>AVERAGE(Q2:Q7)</f>
-        <v>16</v>
-      </c>
-      <c r="X2" t="e">
+        <v>17.333333333333332</v>
+      </c>
+      <c r="X2">
         <f>_xlfn.STDEV.S(Q2:Q7)</f>
-        <v>#DIV/0!</v>
+        <v>4.1912607490666396</v>
       </c>
       <c r="Y2">
         <f>AVERAGE(R2:R7)</f>
-        <v>12.5</v>
-      </c>
-      <c r="Z2" t="e">
+        <v>15.583333333333334</v>
+      </c>
+      <c r="Z2">
         <f>_xlfn.STDEV.S(R2:R7)</f>
-        <v>#DIV/0!</v>
+        <v>2.8533605917701061</v>
       </c>
       <c r="AA2">
         <f>AVERAGE(S2:S7)</f>
-        <v>32.5</v>
-      </c>
-      <c r="AB2" t="e">
+        <v>29.083333333333332</v>
+      </c>
+      <c r="AB2">
         <f>_xlfn.STDEV.S(S2:S7)</f>
-        <v>#DIV/0!</v>
+        <v>4.1882772910430139</v>
       </c>
       <c r="AC2">
         <f>AVERAGE(T2:T7)</f>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="AD2" t="e">
+        <v>20.666666666666668</v>
+      </c>
+      <c r="AD2">
         <f>_xlfn.STDEV.S(T2:T7)</f>
-        <v>#DIV/0!</v>
+        <v>2.7487370837451088</v>
       </c>
       <c r="AE2">
         <f>AVERAGE(V2:V7)</f>
-        <v>7.8333333333333321</v>
-      </c>
-      <c r="AF2" t="e">
+        <v>5.916666666666667</v>
+      </c>
+      <c r="AF2">
         <f>_xlfn.STDEV.S(V2:V7)</f>
-        <v>#DIV/0!</v>
+        <v>1.6012148165967275</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>81</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>19</v>
+      </c>
+      <c r="E3">
+        <v>81</v>
+      </c>
+      <c r="G3">
+        <v>72</v>
+      </c>
+      <c r="H3">
+        <v>28</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>95</v>
+      </c>
+      <c r="L3">
+        <v>62</v>
+      </c>
+      <c r="M3">
+        <v>38</v>
+      </c>
+      <c r="N3">
+        <v>16</v>
+      </c>
+      <c r="O3">
+        <v>84</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q7" si="0">AVERAGE(C3:D3)</f>
+        <v>19</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R7" si="1">AVERAGE(H3:I3)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S7" si="2">AVERAGE(M3:N3)</f>
+        <v>27</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T7" si="3">AVERAGE(Q3:S3)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U7" si="4">MIN(Q3:S3)</f>
+        <v>16.5</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V7" si="5">T3-U3</f>
+        <v>4.3333333333333321</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>91</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>83</v>
+      </c>
+      <c r="G4">
+        <v>87</v>
+      </c>
+      <c r="H4">
+        <v>13</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>90</v>
+      </c>
+      <c r="L4">
+        <v>77</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>30</v>
+      </c>
+      <c r="O4">
+        <v>70</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="2"/>
+        <v>26.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="5"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>84</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+      <c r="E5">
+        <v>75</v>
+      </c>
+      <c r="G5">
+        <v>86</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>86</v>
+      </c>
+      <c r="L5">
+        <v>75</v>
+      </c>
+      <c r="M5">
+        <v>25</v>
+      </c>
+      <c r="N5">
+        <v>27</v>
+      </c>
+      <c r="O5">
+        <v>73</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>6.1666666666666679</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>92</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>85</v>
+      </c>
+      <c r="G6">
+        <v>76</v>
+      </c>
+      <c r="H6">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
+        <v>91</v>
+      </c>
+      <c r="L6">
+        <v>68</v>
+      </c>
+      <c r="M6">
+        <v>32</v>
+      </c>
+      <c r="N6">
+        <v>23</v>
+      </c>
+      <c r="O6">
+        <v>77</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>18.5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>76</v>
+      </c>
+      <c r="G7">
+        <v>75</v>
+      </c>
+      <c r="H7">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>95</v>
+      </c>
+      <c r="L7">
+        <v>67</v>
+      </c>
+      <c r="M7">
+        <v>33</v>
+      </c>
+      <c r="N7">
+        <v>41</v>
+      </c>
+      <c r="O7">
+        <v>59</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>8.3333333333333321</v>
+      </c>
+    </row>
+    <row r="11" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>26</v>
+      </c>
+      <c r="E11">
+        <v>74</v>
+      </c>
+      <c r="G11">
+        <v>77</v>
+      </c>
+      <c r="H11">
+        <v>23</v>
+      </c>
+      <c r="I11">
+        <v>17</v>
+      </c>
+      <c r="J11">
+        <v>83</v>
+      </c>
+      <c r="L11">
+        <v>74</v>
+      </c>
+      <c r="M11">
+        <v>26</v>
+      </c>
+      <c r="N11">
+        <v>35</v>
+      </c>
+      <c r="O11">
+        <v>65</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" ref="Q8:Q16" si="6">AVERAGE(C11:D11)</f>
+        <v>22</v>
+      </c>
+      <c r="R11">
+        <f t="shared" ref="R8:R16" si="7">AVERAGE(H11:I11)</f>
+        <v>20</v>
+      </c>
+      <c r="S11">
+        <f t="shared" ref="S8:S16" si="8">AVERAGE(M11:N11)</f>
+        <v>30.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" ref="T8:T16" si="9">AVERAGE(Q11:S11)</f>
+        <v>24.166666666666668</v>
+      </c>
+      <c r="U11">
+        <f t="shared" ref="U8:U16" si="10">MIN(Q11:S11)</f>
+        <v>20</v>
+      </c>
+      <c r="V11">
+        <f t="shared" ref="V8:V16" si="11">T11-U11</f>
+        <v>4.1666666666666679</v>
+      </c>
+      <c r="W11">
+        <f>AVERAGE(Q11:Q16)</f>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="X11">
+        <f>_xlfn.STDEV.S(Q11:Q16)</f>
+        <v>4.1912607490666396</v>
+      </c>
+      <c r="Y11">
+        <f>AVERAGE(R11:R16)</f>
+        <v>15.666666666666666</v>
+      </c>
+      <c r="Z11">
+        <f>_xlfn.STDEV.S(R11:R16)</f>
+        <v>2.84018778721877</v>
+      </c>
+      <c r="AA11">
+        <f>AVERAGE(S11:S16)</f>
+        <v>28.916666666666668</v>
+      </c>
+      <c r="AB11">
+        <f>_xlfn.STDEV.S(S11:S16)</f>
+        <v>4.3060035609212646</v>
+      </c>
+      <c r="AC11">
+        <f>AVERAGE(T11:T16)</f>
+        <v>20.638888888888889</v>
+      </c>
+      <c r="AD11">
+        <f>_xlfn.STDEV.S(T11:T16)</f>
+        <v>2.7817194256364095</v>
+      </c>
+      <c r="AE11">
+        <f>AVERAGE(V11:V16)</f>
+        <v>5.8055555555555562</v>
+      </c>
+      <c r="AF11">
+        <f>_xlfn.STDEV.S(V11:V16)</f>
+        <v>1.5755657420137719</v>
+      </c>
+    </row>
+    <row r="12" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>81</v>
+      </c>
+      <c r="C12">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>19</v>
+      </c>
+      <c r="E12">
+        <v>81</v>
+      </c>
+      <c r="G12">
+        <v>72</v>
+      </c>
+      <c r="H12">
+        <v>28</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>95</v>
+      </c>
+      <c r="L12">
+        <v>64</v>
+      </c>
+      <c r="M12">
+        <v>36</v>
+      </c>
+      <c r="N12">
+        <v>16</v>
+      </c>
+      <c r="O12">
+        <v>84</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>26</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>20.5</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>91</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>17</v>
+      </c>
+      <c r="E13">
+        <v>83</v>
+      </c>
+      <c r="G13">
+        <v>87</v>
+      </c>
+      <c r="H13">
+        <v>13</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>90</v>
+      </c>
+      <c r="L13">
+        <v>77</v>
+      </c>
+      <c r="M13">
+        <v>23</v>
+      </c>
+      <c r="N13">
+        <v>30</v>
+      </c>
+      <c r="O13">
+        <v>70</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>11.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>26.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="11"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>84</v>
+      </c>
+      <c r="C14">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>75</v>
+      </c>
+      <c r="G14">
+        <v>86</v>
+      </c>
+      <c r="H14">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>14</v>
+      </c>
+      <c r="J14">
+        <v>86</v>
+      </c>
+      <c r="L14">
+        <v>75</v>
+      </c>
+      <c r="M14">
+        <v>25</v>
+      </c>
+      <c r="N14">
+        <v>27</v>
+      </c>
+      <c r="O14">
+        <v>73</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>20.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>26</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="11"/>
+        <v>6.1666666666666679</v>
+      </c>
+    </row>
+    <row r="15" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>92</v>
+      </c>
+      <c r="C15">
+        <v>8</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+      <c r="E15">
+        <v>85</v>
+      </c>
+      <c r="G15">
+        <v>76</v>
+      </c>
+      <c r="H15">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>9</v>
+      </c>
+      <c r="J15">
+        <v>91</v>
+      </c>
+      <c r="L15">
+        <v>68</v>
+      </c>
+      <c r="M15">
+        <v>32</v>
+      </c>
+      <c r="N15">
+        <v>23</v>
+      </c>
+      <c r="O15">
+        <v>77</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>11.5</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="8"/>
+        <v>27.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="9"/>
+        <v>18.5</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>88</v>
+      </c>
+      <c r="C16">
+        <v>12</v>
+      </c>
+      <c r="D16">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>76</v>
+      </c>
+      <c r="G16">
+        <v>74</v>
+      </c>
+      <c r="H16">
+        <v>26</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>95</v>
+      </c>
+      <c r="L16">
+        <v>67</v>
+      </c>
+      <c r="M16">
+        <v>33</v>
+      </c>
+      <c r="N16">
+        <v>41</v>
+      </c>
+      <c r="O16">
+        <v>59</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="7"/>
+        <v>15.5</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="8"/>
+        <v>37</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="9"/>
+        <v>23.5</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="11"/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1381,13 +3808,13 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>9</v>
@@ -1408,22 +3835,22 @@
         <v>12</v>
       </c>
       <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>22</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>23</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
@@ -1500,44 +3927,44 @@
         <v>4.8333333333333321</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q8)</f>
-        <v>17.416666666666668</v>
+        <f>AVERAGE(Q3:Q9)</f>
+        <v>17.071428571428573</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q8)</f>
-        <v>2.1311186420907333</v>
+        <f>_xlfn.STDEV.S(Q3:Q9)</f>
+        <v>2.149196970742242</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R8)</f>
-        <v>17.166666666666668</v>
+        <f>AVERAGE(R3:R9)</f>
+        <v>16.857142857142858</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R8)</f>
-        <v>3.3115957885386087</v>
+        <f>_xlfn.STDEV.S(R3:R9)</f>
+        <v>3.1320159337914957</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S8)</f>
-        <v>31</v>
+        <f>AVERAGE(S3:S9)</f>
+        <v>30.928571428571427</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S8)</f>
-        <v>4.1472882706655438</v>
+        <f>_xlfn.STDEV.S(S3:S9)</f>
+        <v>3.7906526639943623</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T8)</f>
-        <v>21.861111111111111</v>
+        <f>AVERAGE(T3:T9)</f>
+        <v>21.619047619047617</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T8)</f>
-        <v>0.89079656404732477</v>
+        <f>_xlfn.STDEV.S(T3:T9)</f>
+        <v>1.0350983390135315</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V8)</f>
-        <v>5.8611111111111116</v>
+        <f>AVERAGE(V3:V9)</f>
+        <v>5.7619047619047636</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V8)</f>
-        <v>1.8055982900925591</v>
+        <f>_xlfn.STDEV.S(V3:V9)</f>
+        <v>1.6690459207925552</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
@@ -1974,44 +4401,44 @@
         <v>4.8333333333333321</v>
       </c>
       <c r="W12">
-        <f>AVERAGE(Q12:Q17)</f>
-        <v>17.416666666666668</v>
+        <f>AVERAGE(Q12:Q18)</f>
+        <v>17.071428571428573</v>
       </c>
       <c r="X12">
-        <f>_xlfn.STDEV.S(Q12:Q17)</f>
-        <v>2.1311186420907333</v>
+        <f>_xlfn.STDEV.S(Q12:Q18)</f>
+        <v>2.149196970742242</v>
       </c>
       <c r="Y12">
-        <f>AVERAGE(R12:R17)</f>
-        <v>17.166666666666668</v>
+        <f>AVERAGE(R12:R18)</f>
+        <v>16.857142857142858</v>
       </c>
       <c r="Z12">
-        <f>_xlfn.STDEV.S(R12:R17)</f>
-        <v>3.3115957885386087</v>
+        <f>_xlfn.STDEV.S(R12:R18)</f>
+        <v>3.1320159337914957</v>
       </c>
       <c r="AA12">
-        <f>AVERAGE(S12:S17)</f>
-        <v>30.916666666666668</v>
+        <f>AVERAGE(S12:S18)</f>
+        <v>30.857142857142858</v>
       </c>
       <c r="AB12">
-        <f>_xlfn.STDEV.S(S12:S17)</f>
-        <v>4.0300951188112926</v>
+        <f>_xlfn.STDEV.S(S12:S18)</f>
+        <v>3.682325869545477</v>
       </c>
       <c r="AC12">
-        <f>AVERAGE(T12:T17)</f>
-        <v>21.833333333333332</v>
+        <f>AVERAGE(T12:T18)</f>
+        <v>21.595238095238095</v>
       </c>
       <c r="AD12">
-        <f>_xlfn.STDEV.S(T12:T17)</f>
-        <v>0.90676470058236358</v>
+        <f>_xlfn.STDEV.S(T12:T18)</f>
+        <v>1.0401973764678425</v>
       </c>
       <c r="AE12">
-        <f>AVERAGE(V12:V17)</f>
-        <v>5.833333333333333</v>
+        <f>AVERAGE(V12:V18)</f>
+        <v>5.738095238095239</v>
       </c>
       <c r="AF12">
-        <f>_xlfn.STDEV.S(V12:V17)</f>
-        <v>1.7669811040931429</v>
+        <f>_xlfn.STDEV.S(V12:V18)</f>
+        <v>1.6325881033940881</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
@@ -2398,13 +4825,13 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>9</v>
@@ -2425,22 +4852,22 @@
         <v>12</v>
       </c>
       <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>22</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>23</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
@@ -2869,7 +5296,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
@@ -3296,13 +5723,13 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>9</v>
@@ -3323,22 +5750,22 @@
         <v>12</v>
       </c>
       <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>22</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>23</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
@@ -3415,44 +5842,44 @@
         <v>4.6666666666666679</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q8)</f>
-        <v>17.416666666666668</v>
+        <f>AVERAGE(Q3:Q9)</f>
+        <v>17.142857142857142</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q8)</f>
-        <v>1.5942605391424161</v>
+        <f>_xlfn.STDEV.S(Q3:Q9)</f>
+        <v>1.625686668105863</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R8)</f>
-        <v>17.583333333333332</v>
+        <f>AVERAGE(R3:R9)</f>
+        <v>17.142857142857142</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R8)</f>
-        <v>2.7823850680067004</v>
+        <f>_xlfn.STDEV.S(R3:R9)</f>
+        <v>2.7945525240230817</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S8)</f>
-        <v>30.833333333333332</v>
+        <f>AVERAGE(S3:S9)</f>
+        <v>29.571428571428573</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S8)</f>
-        <v>2.6204325342711394</v>
+        <f>_xlfn.STDEV.S(S3:S9)</f>
+        <v>4.1071946166510731</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T8)</f>
-        <v>21.944444444444446</v>
+        <f>AVERAGE(T3:T9)</f>
+        <v>21.285714285714288</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T8)</f>
-        <v>1.8398872751299695</v>
+        <f>_xlfn.STDEV.S(T3:T9)</f>
+        <v>2.4204267409829603</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V8)</f>
-        <v>5.4444444444444455</v>
+        <f>AVERAGE(V3:V9)</f>
+        <v>5.0714285714285712</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V8)</f>
-        <v>1.3608276348795441</v>
+        <f>_xlfn.STDEV.S(V3:V9)</f>
+        <v>1.5865672904720345</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
@@ -3829,7 +6256,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
@@ -3870,68 +6297,68 @@
         <v>77</v>
       </c>
       <c r="Q13">
-        <f t="shared" ref="Q10:Q19" si="6">AVERAGE(C13:D13)</f>
+        <f t="shared" ref="Q13:Q19" si="6">AVERAGE(C13:D13)</f>
         <v>17</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R10:R19" si="7">AVERAGE(H13:I13)</f>
+        <f t="shared" ref="R13:R19" si="7">AVERAGE(H13:I13)</f>
         <v>18.5</v>
       </c>
       <c r="S13">
-        <f t="shared" ref="S10:S19" si="8">AVERAGE(M13:N13)</f>
+        <f t="shared" ref="S13:S19" si="8">AVERAGE(M13:N13)</f>
         <v>27.5</v>
       </c>
       <c r="T13">
-        <f t="shared" ref="T10:T19" si="9">AVERAGE(Q13:S13)</f>
+        <f t="shared" ref="T13:T19" si="9">AVERAGE(Q13:S13)</f>
         <v>21</v>
       </c>
       <c r="U13">
-        <f t="shared" ref="U10:U19" si="10">MIN(Q13:S13)</f>
+        <f t="shared" ref="U13:U19" si="10">MIN(Q13:S13)</f>
         <v>17</v>
       </c>
       <c r="V13">
-        <f t="shared" ref="V10:V19" si="11">T13-U13</f>
+        <f t="shared" ref="V13:V19" si="11">T13-U13</f>
         <v>4</v>
       </c>
       <c r="W13">
-        <f>AVERAGE(Q13:Q18)</f>
-        <v>17.416666666666668</v>
+        <f>AVERAGE(Q13:Q19)</f>
+        <v>17.142857142857142</v>
       </c>
       <c r="X13">
-        <f>_xlfn.STDEV.S(Q13:Q18)</f>
-        <v>1.5942605391424161</v>
+        <f>_xlfn.STDEV.S(Q13:Q19)</f>
+        <v>1.625686668105863</v>
       </c>
       <c r="Y13">
-        <f>AVERAGE(R13:R18)</f>
-        <v>17.916666666666668</v>
+        <f>AVERAGE(R13:R19)</f>
+        <v>17.428571428571427</v>
       </c>
       <c r="Z13">
-        <f>_xlfn.STDEV.S(R13:R18)</f>
-        <v>2.7462095088806775</v>
+        <f>_xlfn.STDEV.S(R13:R19)</f>
+        <v>2.8199966227605597</v>
       </c>
       <c r="AA13">
-        <f>AVERAGE(S13:S18)</f>
-        <v>30.666666666666668</v>
+        <f>AVERAGE(S13:S19)</f>
+        <v>29.428571428571427</v>
       </c>
       <c r="AB13">
-        <f>_xlfn.STDEV.S(S13:S18)</f>
-        <v>3.1251666622224592</v>
+        <f>_xlfn.STDEV.S(S13:S19)</f>
+        <v>4.3438517031601753</v>
       </c>
       <c r="AC13">
-        <f>AVERAGE(T13:T18)</f>
-        <v>22</v>
+        <f>AVERAGE(T13:T19)</f>
+        <v>21.333333333333336</v>
       </c>
       <c r="AD13">
-        <f>_xlfn.STDEV.S(T13:T18)</f>
-        <v>1.8529256146249728</v>
+        <f>_xlfn.STDEV.S(T13:T19)</f>
+        <v>2.443813049769171</v>
       </c>
       <c r="AE13">
-        <f>AVERAGE(V13:V18)</f>
-        <v>5.416666666666667</v>
+        <f>AVERAGE(V13:V19)</f>
+        <v>5.0476190476190466</v>
       </c>
       <c r="AF13">
-        <f>_xlfn.STDEV.S(V13:V18)</f>
-        <v>1.4634434279010153</v>
+        <f>_xlfn.STDEV.S(V13:V19)</f>
+        <v>1.6547190813232469</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
@@ -4318,13 +6745,13 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>9</v>
@@ -4345,22 +6772,22 @@
         <v>12</v>
       </c>
       <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>22</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>23</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
@@ -4789,7 +7216,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
@@ -5220,13 +7647,13 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>9</v>
@@ -5247,22 +7674,22 @@
         <v>12</v>
       </c>
       <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>22</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>23</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
@@ -5691,7 +8118,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
